--- a/12-06-26/furqan.xlsx
+++ b/12-06-26/furqan.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DCD35F9-406F-488A-AA60-1BBF0DF1972A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3EE1D89-1B8A-49EF-9B10-888CB7D4280B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3338,7 +3338,7 @@
       <c r="M4" s="198"/>
       <c r="N4" s="199">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="O4" s="199"/>
       <c r="P4" s="199"/>
@@ -3366,7 +3366,7 @@
       <c r="M5" s="198"/>
       <c r="N5" s="199">
         <f ca="1">N4-1</f>
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="O5" s="197"/>
       <c r="P5" s="197"/>
@@ -3660,12 +3660,10 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="100"/>
-      <c r="H16" s="101">
-        <v>6</v>
-      </c>
+      <c r="H16" s="101"/>
       <c r="I16" s="102">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>314.77499999999998</v>
+        <v>0</v>
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
@@ -3674,23 +3672,23 @@
       </c>
       <c r="L16" s="105">
         <f>I16*8%</f>
-        <v>25.181999999999999</v>
+        <v>0</v>
       </c>
       <c r="M16" s="106">
         <f>I16-K16-L16</f>
-        <v>289.59299999999996</v>
+        <v>0</v>
       </c>
       <c r="N16" s="106">
         <f t="shared" ref="N16:N24" si="0">(M16*$N$15)+(J16*F16)*$N$15</f>
-        <v>63.710459999999991</v>
+        <v>0</v>
       </c>
       <c r="O16" s="107">
         <f>(N16+M16)*$O$15</f>
-        <v>1.7665172999999998</v>
+        <v>0</v>
       </c>
       <c r="P16" s="105">
         <f t="shared" ref="P16:P24" si="1">M16+N16+O16</f>
-        <v>355.06997729999995</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="108"/>
       <c r="XFD16" t="s">
@@ -3722,39 +3720,35 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="114"/>
-      <c r="H17" s="115">
-        <v>18</v>
-      </c>
+      <c r="H17" s="115"/>
       <c r="I17" s="116">
         <f t="shared" ref="I17:I23" si="2">(G17*D17)*F17+H17*F17</f>
-        <v>944.32499999999993</v>
-      </c>
-      <c r="J17" s="117">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J17" s="117"/>
       <c r="K17" s="1">
         <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
         <f t="shared" ref="L17:L21" si="4">I17*8%</f>
-        <v>75.545999999999992</v>
+        <v>0</v>
       </c>
       <c r="M17" s="118">
         <f t="shared" ref="M17:M23" si="5">I17-K17-L17</f>
-        <v>868.779</v>
+        <v>0</v>
       </c>
       <c r="N17" s="118">
         <f t="shared" si="0"/>
-        <v>214.21487999999999</v>
+        <v>0</v>
       </c>
       <c r="O17" s="119">
         <f t="shared" ref="O17:O24" si="6">(N17+M17)*$O$15</f>
-        <v>5.4149694000000004</v>
+        <v>0</v>
       </c>
       <c r="P17" s="120">
         <f t="shared" si="1"/>
-        <v>1088.4088494</v>
+        <v>0</v>
       </c>
       <c r="S17" s="64"/>
       <c r="XFD17" t="s">
@@ -3786,12 +3780,10 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="114"/>
-      <c r="H18" s="115">
-        <v>18</v>
-      </c>
+      <c r="H18" s="115"/>
       <c r="I18" s="116">
         <f t="shared" si="2"/>
-        <v>944.32499999999993</v>
+        <v>0</v>
       </c>
       <c r="J18" s="117"/>
       <c r="K18" s="1">
@@ -3800,23 +3792,23 @@
       </c>
       <c r="L18" s="105">
         <f t="shared" si="4"/>
-        <v>75.545999999999992</v>
+        <v>0</v>
       </c>
       <c r="M18" s="118">
         <f t="shared" si="5"/>
-        <v>868.779</v>
+        <v>0</v>
       </c>
       <c r="N18" s="118">
         <f t="shared" si="0"/>
-        <v>191.13138000000001</v>
+        <v>0</v>
       </c>
       <c r="O18" s="119">
         <f t="shared" si="6"/>
-        <v>5.2995519</v>
+        <v>0</v>
       </c>
       <c r="P18" s="120">
         <f t="shared" si="1"/>
-        <v>1065.2099319000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -3844,12 +3836,10 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="114"/>
-      <c r="H19" s="115">
-        <v>15</v>
-      </c>
+      <c r="H19" s="115"/>
       <c r="I19" s="116">
         <f t="shared" si="2"/>
-        <v>1089.5999999999999</v>
+        <v>0</v>
       </c>
       <c r="J19" s="117"/>
       <c r="K19" s="1">
@@ -3858,23 +3848,23 @@
       </c>
       <c r="L19" s="105">
         <f t="shared" si="4"/>
-        <v>87.167999999999992</v>
+        <v>0</v>
       </c>
       <c r="M19" s="118">
         <f t="shared" si="5"/>
-        <v>1002.4319999999999</v>
+        <v>0</v>
       </c>
       <c r="N19" s="118">
         <f t="shared" si="0"/>
-        <v>220.53503999999998</v>
+        <v>0</v>
       </c>
       <c r="O19" s="119">
         <f t="shared" si="6"/>
-        <v>6.1148351999999999</v>
+        <v>0</v>
       </c>
       <c r="P19" s="120">
         <f t="shared" si="1"/>
-        <v>1229.0818752</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -3902,39 +3892,35 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="114"/>
-      <c r="H20" s="115">
-        <v>15</v>
-      </c>
+      <c r="H20" s="115"/>
       <c r="I20" s="116">
         <f t="shared" si="2"/>
-        <v>1089.5999999999999</v>
-      </c>
-      <c r="J20" s="117">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J20" s="117"/>
       <c r="K20" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L20" s="105">
         <f t="shared" si="4"/>
-        <v>87.167999999999992</v>
+        <v>0</v>
       </c>
       <c r="M20" s="118">
         <f t="shared" si="5"/>
-        <v>1002.4319999999999</v>
+        <v>0</v>
       </c>
       <c r="N20" s="118">
         <f t="shared" si="0"/>
-        <v>252.49663999999999</v>
+        <v>0</v>
       </c>
       <c r="O20" s="119">
         <f t="shared" si="6"/>
-        <v>6.2746431999999999</v>
+        <v>0</v>
       </c>
       <c r="P20" s="120">
         <f t="shared" si="1"/>
-        <v>1261.2032831999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -3962,12 +3948,10 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="114"/>
-      <c r="H21" s="115">
-        <v>15</v>
-      </c>
+      <c r="H21" s="115"/>
       <c r="I21" s="116">
         <f t="shared" si="2"/>
-        <v>1089.5999999999999</v>
+        <v>0</v>
       </c>
       <c r="J21" s="117"/>
       <c r="K21" s="1">
@@ -3976,23 +3960,23 @@
       </c>
       <c r="L21" s="105">
         <f t="shared" si="4"/>
-        <v>87.167999999999992</v>
+        <v>0</v>
       </c>
       <c r="M21" s="118">
         <f t="shared" si="5"/>
-        <v>1002.4319999999999</v>
+        <v>0</v>
       </c>
       <c r="N21" s="118">
         <f t="shared" si="0"/>
-        <v>220.53503999999998</v>
+        <v>0</v>
       </c>
       <c r="O21" s="119">
         <f t="shared" si="6"/>
-        <v>6.1148351999999999</v>
+        <v>0</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="1"/>
-        <v>1229.0818752</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -4178,11 +4162,11 @@
       </c>
       <c r="H25" s="136">
         <f t="shared" si="9"/>
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="I25" s="137">
         <f t="shared" si="9"/>
-        <v>5472.2250000000004</v>
+        <v>0</v>
       </c>
       <c r="J25" s="138"/>
       <c r="K25" s="139">
@@ -4191,23 +4175,23 @@
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>437.77800000000002</v>
+        <v>0</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>5034.4469999999992</v>
+        <v>0</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>1162.6234399999998</v>
+        <v>0</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>30.985352200000001</v>
+        <v>0</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>6228.0557922000007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -4257,7 +4241,7 @@
       <c r="O28" s="235"/>
       <c r="P28" s="152">
         <f>I25</f>
-        <v>5472.2250000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4278,7 +4262,7 @@
       <c r="O29" s="237"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>437.77800000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4321,7 +4305,7 @@
       <c r="O31" s="237"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>5034.4470000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4346,7 +4330,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>1162.6234399999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4368,7 +4352,7 @@
       <c r="O33" s="239"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>6197.0704399999995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -4393,7 +4377,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>30.985352199999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -4403,7 +4387,7 @@
       <c r="O35" s="217"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>6228.0557921999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4575,7 +4559,7 @@
       <c r="M4" s="198"/>
       <c r="N4" s="199">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="O4" s="199"/>
       <c r="P4" s="199"/>
@@ -4603,7 +4587,7 @@
       <c r="M5" s="198"/>
       <c r="N5" s="199">
         <f ca="1">N4-1</f>
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="O5" s="197"/>
       <c r="P5" s="197"/>
@@ -5800,7 +5784,7 @@
       <c r="M4" s="198"/>
       <c r="N4" s="199">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="O4" s="199"/>
       <c r="P4" s="199"/>
@@ -5828,7 +5812,7 @@
       <c r="M5" s="198"/>
       <c r="N5" s="199">
         <f ca="1">N4-1</f>
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="O5" s="197"/>
       <c r="P5" s="197"/>
@@ -7021,7 +7005,7 @@
       <c r="M4" s="198"/>
       <c r="N4" s="199">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="O4" s="199"/>
       <c r="P4" s="199"/>
@@ -7049,7 +7033,7 @@
       <c r="M5" s="198"/>
       <c r="N5" s="199">
         <f ca="1">N4-1</f>
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="O5" s="197"/>
       <c r="P5" s="197"/>
@@ -8242,7 +8226,7 @@
       <c r="M4" s="198"/>
       <c r="N4" s="199">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="O4" s="199"/>
       <c r="P4" s="199"/>
@@ -8270,7 +8254,7 @@
       <c r="M5" s="198"/>
       <c r="N5" s="199">
         <f ca="1">N4-1</f>
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="O5" s="197"/>
       <c r="P5" s="197"/>
@@ -9463,7 +9447,7 @@
       <c r="M4" s="198"/>
       <c r="N4" s="199">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="O4" s="199"/>
       <c r="P4" s="199"/>
@@ -9491,7 +9475,7 @@
       <c r="M5" s="198"/>
       <c r="N5" s="199">
         <f ca="1">N4-1</f>
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="O5" s="197"/>
       <c r="P5" s="197"/>
@@ -10681,7 +10665,7 @@
       <c r="M4" s="198"/>
       <c r="N4" s="199">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="O4" s="199"/>
       <c r="P4" s="199"/>
@@ -10709,7 +10693,7 @@
       <c r="M5" s="198"/>
       <c r="N5" s="199">
         <f ca="1">N4-1</f>
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="O5" s="197"/>
       <c r="P5" s="197"/>
@@ -11898,7 +11882,7 @@
       <c r="M4" s="198"/>
       <c r="N4" s="199">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="O4" s="199"/>
       <c r="P4" s="199"/>
@@ -11926,7 +11910,7 @@
       <c r="M5" s="198"/>
       <c r="N5" s="199">
         <f ca="1">N4-1</f>
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="O5" s="197"/>
       <c r="P5" s="197"/>
@@ -13115,7 +13099,7 @@
       <c r="M4" s="198"/>
       <c r="N4" s="199">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="O4" s="199"/>
       <c r="P4" s="199"/>
@@ -13143,7 +13127,7 @@
       <c r="M5" s="198"/>
       <c r="N5" s="199">
         <f ca="1">N4-1</f>
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="O5" s="197"/>
       <c r="P5" s="197"/>
@@ -14332,7 +14316,7 @@
       <c r="M4" s="198"/>
       <c r="N4" s="199">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="O4" s="199"/>
       <c r="P4" s="199"/>
@@ -14360,7 +14344,7 @@
       <c r="M5" s="198"/>
       <c r="N5" s="199">
         <f ca="1">N4-1</f>
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="O5" s="197"/>
       <c r="P5" s="197"/>
@@ -18299,7 +18283,7 @@
       <c r="M4" s="198"/>
       <c r="N4" s="199">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="O4" s="199"/>
       <c r="P4" s="199"/>
@@ -18327,7 +18311,7 @@
       <c r="M5" s="198"/>
       <c r="N5" s="199">
         <f ca="1">N4-1</f>
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="O5" s="197"/>
       <c r="P5" s="197"/>
@@ -19516,7 +19500,7 @@
       <c r="M4" s="198"/>
       <c r="N4" s="199">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="O4" s="199"/>
       <c r="P4" s="199"/>
@@ -19544,7 +19528,7 @@
       <c r="M5" s="198"/>
       <c r="N5" s="199">
         <f ca="1">N4-1</f>
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="O5" s="197"/>
       <c r="P5" s="197"/>
@@ -20733,7 +20717,7 @@
       <c r="M4" s="198"/>
       <c r="N4" s="199">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="O4" s="199"/>
       <c r="P4" s="199"/>
@@ -20761,7 +20745,7 @@
       <c r="M5" s="198"/>
       <c r="N5" s="199">
         <f ca="1">N4-1</f>
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="O5" s="197"/>
       <c r="P5" s="197"/>
@@ -21950,7 +21934,7 @@
       <c r="M4" s="198"/>
       <c r="N4" s="199">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="O4" s="199"/>
       <c r="P4" s="199"/>
@@ -21978,7 +21962,7 @@
       <c r="M5" s="198"/>
       <c r="N5" s="199">
         <f ca="1">N4-1</f>
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="O5" s="197"/>
       <c r="P5" s="197"/>
@@ -23172,7 +23156,7 @@
       <c r="M4" s="198"/>
       <c r="N4" s="199">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="O4" s="199"/>
       <c r="P4" s="199"/>
@@ -23200,7 +23184,7 @@
       <c r="M5" s="198"/>
       <c r="N5" s="199">
         <f ca="1">N4-1</f>
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="O5" s="197"/>
       <c r="P5" s="197"/>
@@ -23411,7 +23395,7 @@
       </c>
       <c r="U14" s="164">
         <f>+'1'!P35</f>
-        <v>3375.5372160000002</v>
+        <v>0</v>
       </c>
       <c r="XFD14" t="s">
         <v>75</v>
@@ -23497,11 +23481,11 @@
       <c r="G16" s="114"/>
       <c r="H16" s="172">
         <f>+'1'!H16+'2'!H16+'4'!H16+'3'!H16+'5'!H16+'6'!H16+'7'!H16+'8'!H16+'9'!H16+'10'!H16+'11'!H16+'12'!H16</f>
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I16" s="1">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>839.4</v>
+        <v>524.625</v>
       </c>
       <c r="J16" s="172">
         <f>+'1'!J16+'2'!J16+'4'!J16+'3'!J16+'5'!J16+'6'!J16+'7'!J16+'8'!J16+'9'!J16+'10'!J16+'11'!J16+'12'!J16</f>
@@ -23513,23 +23497,23 @@
       </c>
       <c r="L16" s="175">
         <f>+'1'!L16+'2'!L16+'4'!L16+'3'!L16+'5'!L16+'6'!L16+'7'!L16+'8'!L16+'9'!L16+'10'!L16</f>
-        <v>67.152000000000001</v>
+        <v>41.97</v>
       </c>
       <c r="M16" s="106">
         <f>I16-K16-L16</f>
-        <v>772.24799999999993</v>
+        <v>482.65499999999997</v>
       </c>
       <c r="N16" s="101">
         <f>+'1'!N16+'2'!N16+'4'!N16+'3'!N16+'5'!N16+'6'!N16+'7'!N16+'8'!N16+'9'!N16+'10'!N16</f>
-        <v>169.89455999999998</v>
+        <v>106.1841</v>
       </c>
       <c r="O16" s="101">
         <f>+'1'!O16+'2'!O16+'4'!O16+'3'!O16+'5'!O16+'6'!O16+'7'!O16+'8'!O16+'9'!O16+'10'!O16</f>
-        <v>16.487494799999997</v>
+        <v>14.720977499999998</v>
       </c>
       <c r="P16" s="105">
         <f t="shared" ref="P16:P24" si="0">M16+N16+O16</f>
-        <v>958.63005479999993</v>
+        <v>603.56007749999992</v>
       </c>
       <c r="Q16" s="108"/>
       <c r="T16" s="163" t="str">
@@ -23571,15 +23555,15 @@
       <c r="G17" s="114"/>
       <c r="H17" s="172">
         <f>+'1'!H17+'2'!H17+'4'!H17+'3'!H17+'5'!H17+'6'!H17+'7'!H17+'8'!H17+'9'!H17+'10'!H17+'11'!H17+'12'!H17</f>
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="I17" s="1">
         <f t="shared" ref="I17:I23" si="1">(G17*D17)*F17+H17*F17</f>
-        <v>1468.95</v>
+        <v>524.625</v>
       </c>
       <c r="J17" s="172">
         <f>+'1'!J17+'2'!J17+'4'!J17+'3'!J17+'5'!J17+'6'!J17+'7'!J17+'8'!J17+'9'!J17+'10'!J17+'11'!J17+'12'!J17</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K17" s="172">
         <f>+'1'!K17+'2'!K17+'4'!K17+'3'!K17+'5'!K17+'6'!K17+'7'!K17+'8'!K17+'9'!K17+'10'!K17</f>
@@ -23587,23 +23571,23 @@
       </c>
       <c r="L17" s="175">
         <f>+'1'!L17+'2'!L17+'4'!L17+'3'!L17+'5'!L17+'6'!L17+'7'!L17+'8'!L17+'9'!L17+'10'!L17</f>
-        <v>117.51599999999999</v>
+        <v>41.97</v>
       </c>
       <c r="M17" s="118">
         <f t="shared" ref="M17:M23" si="2">I17-K17-L17</f>
-        <v>1351.434</v>
+        <v>482.65499999999997</v>
       </c>
       <c r="N17" s="101">
         <f>+'1'!N17+'2'!N17+'4'!N17+'3'!N17+'5'!N17+'6'!N17+'7'!N17+'8'!N17+'9'!N17+'10'!N17</f>
-        <v>320.39897999999999</v>
+        <v>106.1841</v>
       </c>
       <c r="O17" s="101">
         <f>+'1'!O17+'2'!O17+'4'!O17+'3'!O17+'5'!O17+'6'!O17+'7'!O17+'8'!O17+'9'!O17+'10'!O17</f>
-        <v>20.1359469</v>
+        <v>14.720977499999998</v>
       </c>
       <c r="P17" s="120">
         <f t="shared" si="0"/>
-        <v>1691.9689268999998</v>
+        <v>603.56007749999992</v>
       </c>
       <c r="S17" s="64"/>
       <c r="T17" s="163" t="str">
@@ -23645,11 +23629,11 @@
       <c r="G18" s="114"/>
       <c r="H18" s="172">
         <f>+'1'!H18+'2'!H18+'4'!H18+'3'!H18+'5'!H18+'6'!H18+'7'!H18+'8'!H18+'9'!H18+'10'!H18+'11'!H18+'12'!H18</f>
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="I18" s="1">
         <f t="shared" si="1"/>
-        <v>1259.0999999999999</v>
+        <v>314.77499999999998</v>
       </c>
       <c r="J18" s="172">
         <f>+'1'!J18+'2'!J18+'4'!J18+'3'!J18+'5'!J18+'6'!J18+'7'!J18+'8'!J18+'9'!J18+'10'!J18+'11'!J18+'12'!J18</f>
@@ -23661,23 +23645,23 @@
       </c>
       <c r="L18" s="175">
         <f>+'1'!L18+'2'!L18+'4'!L18+'3'!L18+'5'!L18+'6'!L18+'7'!L18+'8'!L18+'9'!L18+'10'!L18</f>
-        <v>100.72799999999999</v>
+        <v>25.181999999999999</v>
       </c>
       <c r="M18" s="118">
         <f t="shared" si="2"/>
-        <v>1158.3719999999998</v>
+        <v>289.59299999999996</v>
       </c>
       <c r="N18" s="101">
         <f>+'1'!N18+'2'!N18+'4'!N18+'3'!N18+'5'!N18+'6'!N18+'7'!N18+'8'!N18+'9'!N18+'10'!N18</f>
-        <v>254.84183999999999</v>
+        <v>63.710459999999991</v>
       </c>
       <c r="O18" s="101">
         <f>+'1'!O18+'2'!O18+'4'!O18+'3'!O18+'5'!O18+'6'!O18+'7'!O18+'8'!O18+'9'!O18+'10'!O18</f>
-        <v>7.0660691999999994</v>
+        <v>1.7665172999999998</v>
       </c>
       <c r="P18" s="120">
         <f t="shared" si="0"/>
-        <v>1420.2799091999998</v>
+        <v>355.06997729999995</v>
       </c>
       <c r="T18" s="163" t="str">
         <f>+'5'!A5</f>
@@ -23715,11 +23699,11 @@
       <c r="G19" s="114"/>
       <c r="H19" s="172">
         <f>+'1'!H19+'2'!H19+'4'!H19+'3'!H19+'5'!H19+'6'!H19+'7'!H19+'8'!H19+'9'!H19+'10'!H19+'11'!H19+'12'!H19</f>
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="I19" s="1">
         <f t="shared" si="1"/>
-        <v>4794.24</v>
+        <v>2615.04</v>
       </c>
       <c r="J19" s="172">
         <f>+'1'!J19+'2'!J19+'4'!J19+'3'!J19+'5'!J19+'6'!J19+'7'!J19+'8'!J19+'9'!J19+'10'!J19+'11'!J19+'12'!J19</f>
@@ -23731,23 +23715,23 @@
       </c>
       <c r="L19" s="175">
         <f>+'1'!L19+'2'!L19+'4'!L19+'3'!L19+'5'!L19+'6'!L19+'7'!L19+'8'!L19+'9'!L19+'10'!L19</f>
-        <v>383.53920000000005</v>
+        <v>209.20320000000001</v>
       </c>
       <c r="M19" s="118">
         <f t="shared" si="2"/>
-        <v>4410.7007999999996</v>
+        <v>2405.8368</v>
       </c>
       <c r="N19" s="101">
         <f>+'1'!N19+'2'!N19+'4'!N19+'3'!N19+'5'!N19+'6'!N19+'7'!N19+'8'!N19+'9'!N19+'10'!N19</f>
-        <v>986.33497599999998</v>
+        <v>545.26489600000002</v>
       </c>
       <c r="O19" s="101">
         <f>+'1'!O19+'2'!O19+'4'!O19+'3'!O19+'5'!O19+'6'!O19+'7'!O19+'8'!O19+'9'!O19+'10'!O19</f>
-        <v>100.68281727999999</v>
+        <v>63.993806079999999</v>
       </c>
       <c r="P19" s="120">
         <f t="shared" si="0"/>
-        <v>5497.7185932799994</v>
+        <v>3015.0955020800002</v>
       </c>
       <c r="T19" s="163" t="str">
         <f>+'6'!A5</f>
@@ -23785,15 +23769,15 @@
       <c r="G20" s="114"/>
       <c r="H20" s="172">
         <f>+'1'!H20+'2'!H20+'4'!H20+'3'!H20+'5'!H20+'6'!H20+'7'!H20+'8'!H20+'9'!H20+'10'!H20+'11'!H20+'12'!H20</f>
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="I20" s="1">
         <f t="shared" si="1"/>
-        <v>2542.4</v>
+        <v>726.4</v>
       </c>
       <c r="J20" s="172">
         <f>+'1'!J20+'2'!J20+'4'!J20+'3'!J20+'5'!J20+'6'!J20+'7'!J20+'8'!J20+'9'!J20+'10'!J20+'11'!J20+'12'!J20</f>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K20" s="172">
         <f>+'1'!K20+'2'!K20+'4'!K20+'3'!K20+'5'!K20+'6'!K20+'7'!K20+'8'!K20+'9'!K20+'10'!K20</f>
@@ -23801,23 +23785,23 @@
       </c>
       <c r="L20" s="175">
         <f>+'1'!L20+'2'!L20+'4'!L20+'3'!L20+'5'!L20+'6'!L20+'7'!L20+'8'!L20+'9'!L20+'10'!L20</f>
-        <v>203.392</v>
+        <v>58.112000000000002</v>
       </c>
       <c r="M20" s="118">
         <f t="shared" si="2"/>
-        <v>2339.0080000000003</v>
+        <v>668.28800000000001</v>
       </c>
       <c r="N20" s="101">
         <f>+'1'!N20+'2'!N20+'4'!N20+'3'!N20+'5'!N20+'6'!N20+'7'!N20+'8'!N20+'9'!N20+'10'!N20</f>
-        <v>626.44736</v>
+        <v>194.96575999999999</v>
       </c>
       <c r="O20" s="101">
         <f>+'1'!O20+'2'!O20+'4'!O20+'3'!O20+'5'!O20+'6'!O20+'7'!O20+'8'!O20+'9'!O20+'10'!O20</f>
-        <v>49.037811200000007</v>
+        <v>21.581344000000001</v>
       </c>
       <c r="P20" s="120">
         <f t="shared" si="0"/>
-        <v>3014.4931712000002</v>
+        <v>884.835104</v>
       </c>
       <c r="T20" s="163" t="str">
         <f>+'7'!A5</f>
@@ -23825,7 +23809,7 @@
       </c>
       <c r="U20" s="164">
         <f>+'7'!P35</f>
-        <v>6228.0557921999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:21 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
@@ -23855,11 +23839,11 @@
       <c r="G21" s="114"/>
       <c r="H21" s="172">
         <f>+'1'!H21+'2'!H21+'4'!H21+'3'!H21+'5'!H21+'6'!H21+'7'!H21+'8'!H21+'9'!H21+'10'!H21+'11'!H21+'12'!H21</f>
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I21" s="1">
         <f t="shared" si="1"/>
-        <v>4358.3999999999996</v>
+        <v>2179.1999999999998</v>
       </c>
       <c r="J21" s="172">
         <f>+'1'!J21+'2'!J21+'4'!J21+'3'!J21+'5'!J21+'6'!J21+'7'!J21+'8'!J21+'9'!J21+'10'!J21+'11'!J21+'12'!J21</f>
@@ -23871,23 +23855,23 @@
       </c>
       <c r="L21" s="175">
         <f>+'1'!L21+'2'!L21+'4'!L21+'3'!L21+'5'!L21+'6'!L21+'7'!L21+'8'!L21+'9'!L21+'10'!L21</f>
-        <v>348.67200000000003</v>
+        <v>174.33600000000001</v>
       </c>
       <c r="M21" s="118">
         <f t="shared" si="2"/>
-        <v>4009.7279999999996</v>
+        <v>2004.8639999999998</v>
       </c>
       <c r="N21" s="101">
         <f>+'1'!N21+'2'!N21+'4'!N21+'3'!N21+'5'!N21+'6'!N21+'7'!N21+'8'!N21+'9'!N21+'10'!N21</f>
-        <v>882.14016000000004</v>
+        <v>441.07007999999996</v>
       </c>
       <c r="O21" s="101">
         <f>+'1'!O21+'2'!O21+'4'!O21+'3'!O21+'5'!O21+'6'!O21+'7'!O21+'8'!O21+'9'!O21+'10'!O21</f>
-        <v>97.837363199999999</v>
+        <v>61.148352000000003</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="0"/>
-        <v>4989.7055232000002</v>
+        <v>2507.0824320000002</v>
       </c>
       <c r="T21" s="163" t="str">
         <f>+'8'!A5</f>
@@ -24115,7 +24099,7 @@
       <c r="B25" s="223"/>
       <c r="C25" s="224">
         <f>H25/40</f>
-        <v>6.4249999999999998</v>
+        <v>3.25</v>
       </c>
       <c r="D25" s="218"/>
       <c r="E25" s="218"/>
@@ -24126,15 +24110,15 @@
       </c>
       <c r="H25" s="177">
         <f t="shared" si="3"/>
-        <v>257</v>
+        <v>130</v>
       </c>
       <c r="I25" s="178">
         <f t="shared" si="3"/>
-        <v>16360.929999999998</v>
+        <v>7983.1049999999996</v>
       </c>
       <c r="J25" s="177">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K25" s="178">
         <f t="shared" si="3"/>
@@ -24142,23 +24126,23 @@
       </c>
       <c r="L25" s="179">
         <f t="shared" si="3"/>
-        <v>1275.9212000000002</v>
+        <v>605.69520000000011</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="3"/>
-        <v>15046.563399999997</v>
+        <v>7338.9643999999989</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>3461.1738479999999</v>
+        <v>1678.4953680000001</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>321.90221688000008</v>
+        <v>208.58668867999998</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>18829.639464880001</v>
+        <v>9226.0464566800001</v>
       </c>
       <c r="T25" s="163" t="str">
         <f>+'12'!A5</f>
@@ -24190,7 +24174,7 @@
       </c>
       <c r="U26" s="165">
         <f>SUM(U14:U25)</f>
-        <v>18829.639464880001</v>
+        <v>9226.0464566800001</v>
       </c>
     </row>
     <row r="27" spans="1:21 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24223,7 +24207,7 @@
       <c r="O28" s="235"/>
       <c r="P28" s="152">
         <f>I25</f>
-        <v>16360.929999999998</v>
+        <v>7983.1049999999996</v>
       </c>
     </row>
     <row r="29" spans="1:21 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24244,7 +24228,7 @@
       <c r="O29" s="237"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>1275.9212000000002</v>
+        <v>605.69520000000011</v>
       </c>
     </row>
     <row r="30" spans="1:21 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24287,7 +24271,7 @@
       <c r="O31" s="237"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>15046.563399999997</v>
+        <v>7338.9643999999998</v>
       </c>
     </row>
     <row r="32" spans="1:21 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24312,7 +24296,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>3461.1738479999999</v>
+        <v>1678.4953680000001</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24334,7 +24318,7 @@
       <c r="O33" s="239"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>18507.737247999998</v>
+        <v>9017.4597680000006</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24359,7 +24343,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>462.69343119999996</v>
+        <v>225.43649420000003</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24369,7 +24353,7 @@
       <c r="O35" s="217"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>18970.430679199999</v>
+        <v>9242.8962621999999</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24541,7 +24525,7 @@
       <c r="M4" s="198"/>
       <c r="N4" s="199">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="O4" s="199"/>
       <c r="P4" s="199"/>
@@ -24569,7 +24553,7 @@
       <c r="M5" s="198"/>
       <c r="N5" s="199">
         <f ca="1">N4-1</f>
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="O5" s="197"/>
       <c r="P5" s="197"/>
@@ -25039,12 +25023,10 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="114"/>
-      <c r="H19" s="115">
-        <v>15</v>
-      </c>
+      <c r="H19" s="115"/>
       <c r="I19" s="116">
         <f t="shared" si="3"/>
-        <v>1089.5999999999999</v>
+        <v>0</v>
       </c>
       <c r="J19" s="117"/>
       <c r="K19" s="1">
@@ -25053,23 +25035,23 @@
       </c>
       <c r="L19" s="105">
         <f t="shared" si="5"/>
-        <v>87.167999999999992</v>
+        <v>0</v>
       </c>
       <c r="M19" s="118">
         <f t="shared" si="6"/>
-        <v>1002.4319999999999</v>
+        <v>0</v>
       </c>
       <c r="N19" s="118">
         <f t="shared" si="0"/>
-        <v>220.53503999999998</v>
+        <v>0</v>
       </c>
       <c r="O19" s="119">
         <f t="shared" si="1"/>
-        <v>30.574176000000001</v>
+        <v>0</v>
       </c>
       <c r="P19" s="120">
         <f t="shared" si="2"/>
-        <v>1253.5412160000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25097,39 +25079,35 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="114"/>
-      <c r="H20" s="115">
-        <v>10</v>
-      </c>
+      <c r="H20" s="115"/>
       <c r="I20" s="116">
         <f t="shared" si="3"/>
-        <v>726.4</v>
-      </c>
-      <c r="J20" s="117">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J20" s="117"/>
       <c r="K20" s="1">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L20" s="105">
         <f t="shared" si="5"/>
-        <v>58.112000000000002</v>
+        <v>0</v>
       </c>
       <c r="M20" s="118">
         <f t="shared" si="6"/>
-        <v>668.28800000000001</v>
+        <v>0</v>
       </c>
       <c r="N20" s="118">
         <f t="shared" si="0"/>
-        <v>178.98496</v>
+        <v>0</v>
       </c>
       <c r="O20" s="119">
         <f t="shared" si="1"/>
-        <v>21.181824000000002</v>
+        <v>0</v>
       </c>
       <c r="P20" s="120">
         <f t="shared" si="2"/>
-        <v>868.45478400000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25157,12 +25135,10 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="114"/>
-      <c r="H21" s="115">
-        <v>15</v>
-      </c>
+      <c r="H21" s="115"/>
       <c r="I21" s="116">
         <f t="shared" si="3"/>
-        <v>1089.5999999999999</v>
+        <v>0</v>
       </c>
       <c r="J21" s="117"/>
       <c r="K21" s="1">
@@ -25171,23 +25147,23 @@
       </c>
       <c r="L21" s="105">
         <f t="shared" si="5"/>
-        <v>87.167999999999992</v>
+        <v>0</v>
       </c>
       <c r="M21" s="118">
         <f t="shared" si="6"/>
-        <v>1002.4319999999999</v>
+        <v>0</v>
       </c>
       <c r="N21" s="118">
         <f t="shared" si="0"/>
-        <v>220.53503999999998</v>
+        <v>0</v>
       </c>
       <c r="O21" s="119">
         <f t="shared" si="1"/>
-        <v>30.574176000000001</v>
+        <v>0</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="2"/>
-        <v>1253.5412160000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:19 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -25373,11 +25349,11 @@
       </c>
       <c r="H25" s="136">
         <f t="shared" si="9"/>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I25" s="137">
         <f t="shared" si="9"/>
-        <v>2905.6</v>
+        <v>0</v>
       </c>
       <c r="J25" s="138"/>
       <c r="K25" s="139">
@@ -25386,23 +25362,23 @@
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>232.44799999999998</v>
+        <v>0</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>2673.1519999999996</v>
+        <v>0</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>620.05503999999996</v>
+        <v>0</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>82.330175999999994</v>
+        <v>0</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>3375.5372160000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25452,7 +25428,7 @@
       <c r="O28" s="235"/>
       <c r="P28" s="152">
         <f>I25</f>
-        <v>2905.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25473,7 +25449,7 @@
       <c r="O29" s="237"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>232.44799999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25516,7 +25492,7 @@
       <c r="O31" s="237"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>2673.152</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25541,7 +25517,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>620.05503999999996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25563,7 +25539,7 @@
       <c r="O33" s="239"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>3293.2070400000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -25588,7 +25564,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>82.330176000000009</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -25598,7 +25574,7 @@
       <c r="O35" s="217"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>3375.5372160000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -25770,7 +25746,7 @@
       <c r="M4" s="198"/>
       <c r="N4" s="199">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="O4" s="199"/>
       <c r="P4" s="199"/>
@@ -25798,7 +25774,7 @@
       <c r="M5" s="198"/>
       <c r="N5" s="199">
         <f ca="1">N4-1</f>
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="O5" s="197"/>
       <c r="P5" s="197"/>
@@ -26993,7 +26969,7 @@
       <c r="M4" s="198"/>
       <c r="N4" s="199">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="O4" s="199"/>
       <c r="P4" s="199"/>
@@ -27021,7 +26997,7 @@
       <c r="M5" s="198"/>
       <c r="N5" s="199">
         <f ca="1">N4-1</f>
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="O5" s="197"/>
       <c r="P5" s="197"/>
@@ -28225,7 +28201,7 @@
       <c r="M4" s="198"/>
       <c r="N4" s="199">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="O4" s="199"/>
       <c r="P4" s="199"/>
@@ -28253,7 +28229,7 @@
       <c r="M5" s="198"/>
       <c r="N5" s="199">
         <f ca="1">N4-1</f>
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="O5" s="197"/>
       <c r="P5" s="197"/>
@@ -29454,7 +29430,7 @@
       <c r="M4" s="198"/>
       <c r="N4" s="199">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="O4" s="199"/>
       <c r="P4" s="199"/>
@@ -29482,7 +29458,7 @@
       <c r="M5" s="198"/>
       <c r="N5" s="199">
         <f ca="1">N4-1</f>
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="O5" s="197"/>
       <c r="P5" s="197"/>
@@ -30677,7 +30653,7 @@
       <c r="M4" s="198"/>
       <c r="N4" s="199">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="O4" s="199"/>
       <c r="P4" s="199"/>
@@ -30705,7 +30681,7 @@
       <c r="M5" s="198"/>
       <c r="N5" s="199">
         <f ca="1">N4-1</f>
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="O5" s="197"/>
       <c r="P5" s="197"/>
